--- a/product_upload/packages/59/file.xlsx
+++ b/product_upload/packages/59/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -825,6 +830,11 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>DAYVIGO</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-12E51B1DFC3E</t>
         </is>
@@ -845,7 +855,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -997,6 +1007,11 @@
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>DAYVIGO</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-12CEDB8F40B6</t>
         </is>
@@ -1017,7 +1032,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1185,6 +1200,11 @@
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Ryzodeg FlexPen</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-B541F4BEF4B6</t>
         </is>
@@ -1205,7 +1225,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1377,6 +1397,11 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Tresiba FlexPen</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-126DC70E295F</t>
         </is>
@@ -1397,7 +1422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1553,6 +1578,11 @@
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Byraza Plus</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-94B2A4E45BFC</t>
         </is>
@@ -1573,7 +1603,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1733,6 +1763,11 @@
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>Movapo</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-3CA4038CB8F2</t>
         </is>
@@ -1753,7 +1788,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,6 +1954,11 @@
         </is>
       </c>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>Meteospasmyl</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-2E05436F3B17</t>
         </is>
@@ -1939,7 +1979,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2109,6 +2149,11 @@
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>Trelegy Ellipta</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-9E549BB90656</t>
         </is>
@@ -2129,7 +2174,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2289,6 +2334,11 @@
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Acetazolamide</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-FF0E4C8B8BD1</t>
         </is>
@@ -2309,7 +2359,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2465,6 +2515,11 @@
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Varoxa</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-0248DDB3E7C4</t>
         </is>
@@ -2485,7 +2540,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2645,6 +2700,11 @@
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>Ticagrelor</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-94FDDECF1B1A</t>
         </is>
@@ -2665,7 +2725,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2831,6 +2891,11 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Zextro</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-DEC5A418065C</t>
         </is>
@@ -2851,7 +2916,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3011,6 +3076,11 @@
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Aubomide</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-DDE815EA3AFD</t>
         </is>
@@ -3031,7 +3101,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3195,6 +3265,11 @@
         </is>
       </c>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Oxintel</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-C1559AA09C38</t>
         </is>
@@ -3215,7 +3290,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3375,6 +3450,11 @@
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>SITALIX</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-E3558BE97E32</t>
         </is>
@@ -3395,7 +3475,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3547,6 +3627,11 @@
       <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>Sitamend</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-927A5A569A6F</t>
         </is>
@@ -3567,7 +3652,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3723,6 +3808,11 @@
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>Acumig</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-68ECCEDA8F82</t>
         </is>
@@ -3743,7 +3833,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3903,6 +3993,11 @@
         </is>
       </c>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>Acumig</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-5EEC04380AEE</t>
         </is>
@@ -3923,7 +4018,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4079,6 +4174,11 @@
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Sitamend</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-22A4820FCE12</t>
         </is>
@@ -4099,7 +4199,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4259,6 +4359,11 @@
         </is>
       </c>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>Lexipia</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-C2212D1D94A2</t>
         </is>
@@ -4279,7 +4384,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4431,6 +4536,11 @@
       <c r="AR22" t="inlineStr"/>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>Lexipia</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-AB14E7CB8F97</t>
         </is>
@@ -4451,7 +4561,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4611,6 +4721,11 @@
         </is>
       </c>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>baclocan</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-8B63A6EC4685</t>
         </is>
@@ -4631,7 +4746,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4791,6 +4906,11 @@
         </is>
       </c>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>Polygynax</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-B798B20DC423</t>
         </is>
@@ -4811,7 +4931,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4981,6 +5101,11 @@
         </is>
       </c>
       <c r="AT25" t="inlineStr">
+        <is>
+          <t>Alatript</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>SKU-92CB2CE4D8C7</t>
         </is>
@@ -5001,7 +5126,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5171,6 +5296,11 @@
         </is>
       </c>
       <c r="AT26" t="inlineStr">
+        <is>
+          <t>Alatript</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>SKU-A64F1F4AF655</t>
         </is>
@@ -5191,7 +5321,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5357,6 +5487,11 @@
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
+        <is>
+          <t>Alatript</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>SKU-7837654304D4</t>
         </is>
@@ -5377,7 +5512,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5537,6 +5672,11 @@
         </is>
       </c>
       <c r="AT28" t="inlineStr">
+        <is>
+          <t>Lexipia</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>SKU-AFA7CB10E841</t>
         </is>
@@ -5557,7 +5697,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5717,6 +5857,11 @@
         </is>
       </c>
       <c r="AT29" t="inlineStr">
+        <is>
+          <t>Brevie</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>SKU-A8B4A885E27F</t>
         </is>
@@ -5737,7 +5882,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5889,6 +6034,11 @@
       <c r="AR30" t="inlineStr"/>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Brevie</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-930AF36BF958</t>
         </is>
@@ -5909,7 +6059,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6062,6 +6212,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Speranta</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-6D258F8C31A9</t>
         </is>
       </c>
@@ -6081,7 +6236,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6237,6 +6392,11 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>Acumig</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-A14B4FDD9A60</t>
         </is>
@@ -6257,7 +6417,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6413,6 +6573,11 @@
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t>Acumig</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-6FA62CF23062</t>
         </is>
@@ -6433,7 +6598,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6591,6 +6756,11 @@
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
+        <is>
+          <t>Vumerity</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>SKU-83E44F5AD360</t>
         </is>
@@ -6611,7 +6781,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6760,6 +6930,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Dimex</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-373E580E3A62</t>
         </is>
       </c>
@@ -6779,7 +6954,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6943,6 +7118,11 @@
         </is>
       </c>
       <c r="AT36" t="inlineStr">
+        <is>
+          <t>Salofalk</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
         <is>
           <t>SKU-7155759B182B</t>
         </is>
@@ -6963,7 +7143,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7123,6 +7303,11 @@
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
+        <is>
+          <t>Salofalk</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
         <is>
           <t>SKU-8ABABD8B1518</t>
         </is>
@@ -7143,7 +7328,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7303,6 +7488,11 @@
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
+        <is>
+          <t>Salofalk</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>SKU-51793F8D68F7</t>
         </is>
@@ -7323,7 +7513,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7491,6 +7681,11 @@
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
+        <is>
+          <t>Salofalk</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>SKU-57B68688F70C</t>
         </is>
@@ -7511,7 +7706,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7671,6 +7866,11 @@
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
+        <is>
+          <t>Mycophenolate Mofetil Marcan</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
         <is>
           <t>SKU-CD2EDC09A3F2</t>
         </is>
@@ -7691,7 +7891,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7847,6 +8047,11 @@
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Yuflyma</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-A62D2A3BD953</t>
         </is>
@@ -7867,7 +8072,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8025,6 +8230,11 @@
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>Dexrofex</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-E14B02508883</t>
         </is>
@@ -8045,7 +8255,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8201,6 +8411,11 @@
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t>Dexrofex</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-CAC85916798F</t>
         </is>
@@ -8221,7 +8436,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8377,6 +8592,11 @@
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Dexrofex</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-2EC6DB532B89</t>
         </is>
@@ -8397,7 +8617,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8553,6 +8773,11 @@
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Clodreb</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-4C8A4D559686</t>
         </is>
@@ -8573,7 +8798,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8718,6 +8943,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Clodreb</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-DBC357E6E3B3</t>
         </is>
       </c>
@@ -8737,7 +8967,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8893,6 +9123,11 @@
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>Clodreb</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-8C87645BC33E</t>
         </is>
@@ -8913,7 +9148,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9075,6 +9310,11 @@
         </is>
       </c>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Olaparib BOS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-E3D83B535EFF</t>
         </is>
@@ -9095,7 +9335,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9251,6 +9491,11 @@
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>Sitfort</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-7F750A7BFC45</t>
         </is>
@@ -9271,7 +9516,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9420,6 +9665,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Fluxetyl</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-776026F4FF33</t>
         </is>
       </c>
@@ -9439,7 +9689,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9599,6 +9849,11 @@
         </is>
       </c>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-B97C96F34D6E</t>
         </is>
@@ -9619,7 +9874,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9771,6 +10026,11 @@
       <c r="AR52" t="inlineStr"/>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>Provecta</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-425747F90306</t>
         </is>
@@ -9791,7 +10051,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9951,6 +10211,11 @@
         </is>
       </c>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>Dunarez</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-95A820D2D0CA</t>
         </is>
@@ -9971,7 +10236,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10127,6 +10392,11 @@
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Dunarez</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-7381208A319F</t>
         </is>
@@ -10147,7 +10417,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10303,6 +10573,11 @@
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t>Gupisone</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-A162520E77E4</t>
         </is>
@@ -10323,7 +10598,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10479,6 +10754,11 @@
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t>Xadago</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-C78FFE9822B2</t>
         </is>
@@ -10499,7 +10779,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10658,6 +10938,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Plasma-Lyte 148 (pH 7.4)</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-E0A56DC80F8E</t>
         </is>
       </c>
@@ -10677,7 +10962,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10837,6 +11122,11 @@
         </is>
       </c>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>Donfer</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-9BA35CD68E20</t>
         </is>
@@ -10857,7 +11147,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11013,6 +11303,11 @@
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>Donfer</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-BD0B5BD4BB60</t>
         </is>
@@ -11033,7 +11328,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11193,6 +11488,11 @@
         </is>
       </c>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>Sitaglu</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-4C2BE24D6301</t>
         </is>
@@ -11213,7 +11513,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11369,6 +11669,11 @@
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Sitaglu</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-E5FF1545AA47</t>
         </is>
@@ -11389,7 +11694,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11549,6 +11854,11 @@
         </is>
       </c>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Sitaglu</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-268DD9AED4AA</t>
         </is>
@@ -11569,7 +11879,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11720,6 +12030,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Quillivant XR</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-4681B88AE1F3</t>
         </is>
       </c>
@@ -11739,7 +12054,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -11895,6 +12210,11 @@
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Quillivant XR</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-10A1CE753D42</t>
         </is>
@@ -11915,7 +12235,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12073,6 +12393,11 @@
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
+        <is>
+          <t>Quillivant XR</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
         <is>
           <t>SKU-D5D4606990DA</t>
         </is>
@@ -12093,7 +12418,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12257,6 +12582,11 @@
         </is>
       </c>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Cialis</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-24BA0C2E6074</t>
         </is>
@@ -12277,7 +12607,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12441,6 +12771,11 @@
         </is>
       </c>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Senso</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-19D18255B1CF</t>
         </is>
@@ -12461,7 +12796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12613,6 +12948,11 @@
       <c r="AR68" t="inlineStr"/>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>Hydralazine Sciegen</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-480DC28ADFE0</t>
         </is>
@@ -12633,7 +12973,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12793,6 +13133,11 @@
         </is>
       </c>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>Hydralazine Sciegen</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-11EB030887CE</t>
         </is>
@@ -12813,7 +13158,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -12969,6 +13314,11 @@
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Amilian</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-9758C7D91255</t>
         </is>
@@ -12989,7 +13339,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13147,6 +13497,11 @@
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Amilian</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-599AB8898253</t>
         </is>
@@ -13167,7 +13522,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13323,6 +13678,11 @@
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
+        <is>
+          <t>Amilian</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>SKU-31492BFCDA01</t>
         </is>
@@ -13343,7 +13703,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13504,6 +13864,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Ebglyss</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-D44FAB4358D3</t>
         </is>
       </c>
@@ -13523,7 +13888,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13680,6 +14045,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Ocuotan Plus</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-215230DE44A3</t>
         </is>
       </c>
@@ -13699,7 +14069,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -13855,6 +14225,11 @@
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Sefarix</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-01F41A22EE0C</t>
         </is>
@@ -13875,7 +14250,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14034,6 +14409,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Metoject</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-95977D4F0C82</t>
         </is>
       </c>
@@ -14053,7 +14433,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14210,6 +14590,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Metoject</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-7F077AF2DB27</t>
         </is>
       </c>
@@ -14229,7 +14614,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14385,6 +14770,11 @@
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Restain</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-2BF62C11A114</t>
         </is>
@@ -14405,7 +14795,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14571,6 +14961,11 @@
         </is>
       </c>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Sola D3</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-B81D30AFDBCC</t>
         </is>
@@ -14591,7 +14986,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14753,6 +15148,11 @@
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t>Sola D3</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-C80EED80B874</t>
         </is>
@@ -14773,7 +15173,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -14931,6 +15331,11 @@
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falofil </t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-48EECCA4D5E3</t>
         </is>
@@ -14951,7 +15356,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15114,6 +15519,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Tremfya</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-A7EA40BBE554</t>
         </is>
       </c>
@@ -15133,7 +15543,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15289,6 +15699,11 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Veggie Vitamin D3</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-33D715B3EAB0</t>
         </is>
@@ -15309,7 +15724,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15475,6 +15890,11 @@
         </is>
       </c>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-33ABDBF978F0</t>
         </is>
@@ -15495,7 +15915,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15661,6 +16081,11 @@
         </is>
       </c>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-2B45CE48AEA4</t>
         </is>
@@ -15681,7 +16106,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -15843,6 +16268,11 @@
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-94A0DDA4A77D</t>
         </is>
@@ -15863,7 +16293,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16025,6 +16455,11 @@
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-58ED149D777F</t>
         </is>
@@ -16045,7 +16480,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16207,6 +16642,11 @@
         </is>
       </c>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>Promazi</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-76D237AA26E4</t>
         </is>
@@ -16227,7 +16667,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16388,6 +16828,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Nucala</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-7349B25C7A74</t>
         </is>
       </c>
@@ -16407,7 +16852,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16568,6 +17013,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Pafinur</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-18C7EC378C94</t>
         </is>
       </c>
@@ -16587,7 +17037,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16749,6 +17199,11 @@
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>Endura</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-3943EBC94E69</t>
         </is>
@@ -16769,7 +17224,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -16935,6 +17390,11 @@
         </is>
       </c>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>Endura</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-CE8EA34DB310</t>
         </is>
@@ -16955,7 +17415,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17111,6 +17571,11 @@
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Risek Plus</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-9822D1D4D6AF</t>
         </is>
@@ -17131,7 +17596,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17283,6 +17748,11 @@
       <c r="AR94" t="inlineStr"/>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>Rufzel</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-DEC1311CF742</t>
         </is>
@@ -17303,7 +17773,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17459,6 +17929,11 @@
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Rufzel</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-396DC4AB7BF6</t>
         </is>
@@ -17479,7 +17954,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17635,6 +18110,11 @@
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Promazi</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-0287C78E975E</t>
         </is>
@@ -17655,7 +18135,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -17815,6 +18295,11 @@
         </is>
       </c>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Itranox</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-F01B36F387C7</t>
         </is>
@@ -17835,7 +18320,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -17992,6 +18477,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Sildenafil Amarox</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-93E065006C79</t>
         </is>
       </c>
@@ -18011,7 +18501,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18167,6 +18657,11 @@
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tadalafil SPI</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-318D5F4D1783</t>
         </is>
@@ -18187,7 +18682,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18347,6 +18842,11 @@
         </is>
       </c>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t>Tadalafil SPI</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-C07194ADCB00</t>
         </is>
@@ -18367,7 +18867,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18519,6 +19019,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Toxefro</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-ACF6C97BFD69</t>
         </is>
@@ -18535,7 +19040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18581,100 +19086,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18706,7 +19216,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18721,92 +19231,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-77660</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>411.46</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>585</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -18838,7 +19353,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -18853,92 +19368,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-86513</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>97.92</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>586</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -18970,7 +19490,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -18985,92 +19505,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-15200</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>330.43</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>587</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19102,7 +19627,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19117,92 +19642,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-18931</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>29.28</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>588</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19234,7 +19764,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19249,92 +19779,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-41868</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>149.39</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>589</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19366,7 +19901,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19381,92 +19916,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-76454</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>471.03</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>590</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19498,7 +20038,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19513,92 +20053,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-91168</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>376.49</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>591</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19630,7 +20175,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19645,92 +20190,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-93270</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>436.89</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>592</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19762,7 +20312,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19777,92 +20327,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-56393</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>436.35</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>593</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19894,7 +20449,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -19909,92 +20464,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-32402</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>143.3</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>594</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20026,7 +20586,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20041,92 +20601,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-70929</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>177.14</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>595</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20143,7 +20708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20249,6 +20814,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20284,7 +20859,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20349,6 +20924,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-27DA815EEC57</t>
         </is>
@@ -20385,7 +20970,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20450,6 +21035,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-96E9CE159F2A</t>
         </is>
@@ -20486,7 +21081,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20551,6 +21146,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-CE306A7D139F</t>
         </is>
@@ -20587,7 +21192,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20652,6 +21257,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-B436946C9AA9</t>
         </is>
@@ -20688,7 +21303,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -20753,6 +21368,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-EDABFC727E36</t>
         </is>
@@ -20789,7 +21414,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -20854,6 +21479,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-A1338D7205FE</t>
         </is>
@@ -20890,7 +21525,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -20955,6 +21590,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-F059534F1D83</t>
         </is>
@@ -20991,7 +21636,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21056,6 +21701,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-5D95E9805167</t>
         </is>
@@ -21092,7 +21747,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21157,6 +21812,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-798D34171280</t>
         </is>
@@ -21193,7 +21858,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21258,6 +21923,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-005E5AFE0F0B</t>
         </is>
@@ -21294,7 +21969,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21359,6 +22034,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-0CFF2333D771</t>
         </is>
@@ -21395,7 +22080,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21460,6 +22145,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-FF6DE2D7A9C9</t>
         </is>
@@ -21496,7 +22191,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21561,6 +22256,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-680F199BD42F</t>
         </is>
@@ -21597,7 +22302,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21662,6 +22367,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-3B2283BFE2ED</t>
         </is>
@@ -21698,7 +22413,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21763,6 +22478,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A8A07CC73DE9</t>
         </is>
@@ -21799,7 +22524,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -21864,6 +22589,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-1A3765F39166</t>
         </is>
@@ -21900,7 +22635,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -21965,6 +22700,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-A458F044142F</t>
         </is>
@@ -22001,7 +22746,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22066,6 +22811,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-DBE19EEBAEFE</t>
         </is>
@@ -22102,7 +22857,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22167,6 +22922,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-FF2FCA627438</t>
         </is>
@@ -22203,7 +22968,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22268,6 +23033,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-7AA33EB6950F</t>
         </is>

--- a/product_upload/packages/59/file.xlsx
+++ b/product_upload/packages/59/file.xlsx
@@ -682,8 +682,16 @@
           <t>1700865380-335-542056466094</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAYVIGO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DAYVIGO detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -863,8 +871,16 @@
           <t>1584944740-573-352999046014</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DAYVIGO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DAYVIGO detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1430,8 +1446,16 @@
           <t>2825445914-052-934939693740</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Byraza Plus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Byraza Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1611,8 +1635,16 @@
           <t>5122561182-529-055083260263</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Movapo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Movapo detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1796,8 +1828,16 @@
           <t>6166086180-906-485398868590</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Meteospasmyl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Meteospasmyl detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2182,8 +2222,16 @@
           <t>6559764557-504-612329198816</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acetazolamide</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Acetazolamide detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2367,8 +2415,16 @@
           <t>9887939647-502-024636942435</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Varoxa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Varoxa detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2548,8 +2604,16 @@
           <t>3725615941-766-028561324595</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ticagrelor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ticagrelor detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2733,8 +2797,16 @@
           <t>3686052867-657-485094180532</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zextro</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Zextro detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2924,8 +2996,16 @@
           <t>1665314495-468-693524715321</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aubomide</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Aubomide detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3109,8 +3189,16 @@
           <t>6985155834-460-283060713194</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Oxintel</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Oxintel detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3298,8 +3386,16 @@
           <t>8896598109-318-649837773702</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SITALIX</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SITALIX detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3483,8 +3579,16 @@
           <t>1568993930-759-417608850193</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitamend</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sitamend detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3660,8 +3764,16 @@
           <t>3339116033-854-098231804857</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acumig</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Acumig detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3841,8 +3953,16 @@
           <t>3301224044-114-552049541880</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acumig</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Acumig detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4026,8 +4146,16 @@
           <t>0185072378-759-700859640742</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitamend</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sitamend detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4207,8 +4335,16 @@
           <t>6625255637-537-795839000464</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lexipia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lexipia detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4392,8 +4528,16 @@
           <t>0696506093-860-537245386894</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lexipia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Lexipia detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4569,8 +4713,16 @@
           <t>3631290840-740-234242507141</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ baclocan</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>baclocan detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4754,8 +4906,16 @@
           <t>0517469879-934-644088596443</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Polygynax</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Polygynax detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5520,8 +5680,16 @@
           <t>9011528254-434-231140564475</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lexipia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Lexipia detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5705,8 +5873,16 @@
           <t>2804943605-953-267162064881</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Brevie</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Brevie detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5890,8 +6066,16 @@
           <t>4134524391-304-490790641362</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Brevie</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Brevie detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6067,8 +6251,16 @@
           <t>9559824472-542-747613804382</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Speranta</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Speranta detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6244,8 +6436,16 @@
           <t>5999640125-217-444799023959</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acumig</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Acumig detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6425,8 +6625,16 @@
           <t>2887275995-031-944649972927</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Acumig</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Acumig detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6606,8 +6814,16 @@
           <t>7638096280-905-990922964708</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vumerity</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vumerity detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6789,8 +7005,16 @@
           <t>5100020756-766-629624268842</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dimex</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dimex detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -6962,8 +7186,16 @@
           <t>3214584773-943-520014892339</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Salofalk</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Salofalk detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7151,8 +7383,16 @@
           <t>0694535432-255-958664199757</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Salofalk</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Salofalk detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7336,8 +7576,16 @@
           <t>3460274177-562-321929682779</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Salofalk</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Salofalk detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7714,8 +7962,16 @@
           <t>3851174537-599-447507236955</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mycophenolate Mofetil Marcan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Mycophenolate Mofetil Marcan detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7899,8 +8155,16 @@
           <t>0069619746-020-018575022162</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Yuflyma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Yuflyma detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8080,8 +8344,16 @@
           <t>3012596019-799-402164835030</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dexrofex</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Dexrofex detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8263,8 +8535,16 @@
           <t>7006522493-137-214871132322</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dexrofex</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Dexrofex detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8444,8 +8724,16 @@
           <t>2297994273-184-708869512598</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dexrofex</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Dexrofex detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8625,8 +8913,16 @@
           <t>5060841484-109-022896915983</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clodreb</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Clodreb detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8806,8 +9102,16 @@
           <t>7599353555-826-477900054349</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clodreb</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Clodreb detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -8975,8 +9279,16 @@
           <t>2836438180-040-242904678420</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Clodreb</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Clodreb detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9156,8 +9468,16 @@
           <t>2084575565-774-807569190795</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olaparib BOS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Olaparib BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9343,8 +9663,16 @@
           <t>3918474896-708-872946027632</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitfort</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sitfort detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9524,8 +9852,16 @@
           <t>4294392202-442-569669449474</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fluxetyl</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Fluxetyl detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9697,8 +10033,16 @@
           <t>9507812458-047-938988969655</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -9882,8 +10226,16 @@
           <t>6546875467-190-840526764355</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Provecta</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Provecta detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10059,8 +10411,16 @@
           <t>7707247418-790-764787008304</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dunarez</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Dunarez detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10244,8 +10604,16 @@
           <t>5784096667-647-765478314804</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dunarez</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Dunarez detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10425,8 +10793,16 @@
           <t>4942536413-263-932916306035</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gupisone</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Gupisone detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10606,8 +10982,16 @@
           <t>7115193315-396-747872186159</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xadago</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Xadago detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10787,8 +11171,16 @@
           <t>4156941530-675-307884812754</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Plasma-Lyte 148 (pH 7.4)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Plasma-Lyte 148 (pH 7.4) detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -10970,8 +11362,16 @@
           <t>4771437468-289-901268091436</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Donfer</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Donfer detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11155,8 +11555,16 @@
           <t>6773838347-173-831255720203</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Donfer</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Donfer detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11336,8 +11744,16 @@
           <t>7050124137-833-665088398261</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitaglu</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sitaglu detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11521,8 +11937,16 @@
           <t>5453794185-858-138547288948</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitaglu</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sitaglu detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11702,8 +12126,16 @@
           <t>0540927546-211-189127221047</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitaglu</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sitaglu detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -11887,8 +12319,16 @@
           <t>7807820871-786-121381460970</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quillivant XR</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Quillivant XR detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12062,8 +12502,16 @@
           <t>0644066852-463-905535170614</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quillivant XR</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Quillivant XR detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12243,8 +12691,16 @@
           <t>5178816769-520-286058615540</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Quillivant XR</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Quillivant XR detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12426,8 +12882,16 @@
           <t>7167400072-513-069023939000</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cialis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Cialis detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12615,8 +13079,16 @@
           <t>9636048075-072-490209082079</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Senso</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Senso detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -12804,8 +13276,16 @@
           <t>5114337116-315-439269300312</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hydralazine Sciegen</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Hydralazine Sciegen detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -12981,8 +13461,16 @@
           <t>3914818961-453-299020048880</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hydralazine Sciegen</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Hydralazine Sciegen detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13166,8 +13654,16 @@
           <t>3260876846-430-786499064265</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amilian</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Amilian detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13347,8 +13843,16 @@
           <t>4596197986-541-159187459274</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amilian</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Amilian detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13530,8 +14034,16 @@
           <t>4013985361-502-944888203034</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Amilian</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Amilian detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13896,8 +14408,16 @@
           <t>6909438393-993-471453811811</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ocuotan Plus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ocuotan Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14077,8 +14597,16 @@
           <t>2583479646-164-403294163289</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sefarix</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sefarix detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14258,8 +14786,16 @@
           <t>0366662171-265-708607756691</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Metoject</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Metoject detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14441,8 +14977,16 @@
           <t>7411572610-955-693394167002</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Metoject</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Metoject detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14622,8 +15166,16 @@
           <t>5055822660-317-371991070408</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Restain</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Restain detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -14803,8 +15355,16 @@
           <t>2681668149-407-255715533322</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sola D3</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sola D3 detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -14994,8 +15554,16 @@
           <t>5913799819-074-758207898686</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sola D3</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sola D3 detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15181,8 +15749,16 @@
           <t>1352268482-797-740605522395</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Falofil</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Falofil detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15364,8 +15940,16 @@
           <t>4275890646-255-752053979367</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tremfya</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Tremfya detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15551,8 +16135,16 @@
           <t>7530505028-164-556270935552</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Veggie Vitamin D3</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Veggie Vitamin D3 detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -15732,8 +16324,16 @@
           <t>1624207991-997-852385356550</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Volcardy Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -15923,8 +16523,16 @@
           <t>3384587333-338-908312651087</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Volcardy Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16114,8 +16722,16 @@
           <t>0754870500-159-428067959384</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Volcardy Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16301,8 +16917,16 @@
           <t>9059210596-258-574302718940</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Volcardy Plus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Volcardy Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16488,8 +17112,16 @@
           <t>4532131011-695-204177520476</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Promazi</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Promazi detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16675,8 +17307,16 @@
           <t>4071026414-333-239928370554</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Nucala</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Nucala detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -16860,8 +17500,16 @@
           <t>5597634396-578-340048467882</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pafinur</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Pafinur detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17045,8 +17693,16 @@
           <t>5961198221-818-358943313628</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Endura</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Endura detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17232,8 +17888,16 @@
           <t>8516686089-474-784165229379</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Endura</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Endura detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17423,8 +18087,16 @@
           <t>9995404086-540-159356906592</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Risek Plus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Risek Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17604,8 +18276,16 @@
           <t>1233577364-676-649864205307</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rufzel</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Rufzel detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -17781,8 +18461,16 @@
           <t>3796718638-175-798461739040</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rufzel</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Rufzel detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -17962,8 +18650,16 @@
           <t>6471005916-098-544116897561</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Promazi</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Promazi detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18143,8 +18839,16 @@
           <t>6998007155-696-407714414314</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Itranox</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Itranox detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18328,8 +19032,16 @@
           <t>2517522561-440-305476885877</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sildenafil Amarox</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sildenafil Amarox detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18509,8 +19221,16 @@
           <t>3181006720-654-062334052578</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalafil SPI</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Tadalafil SPI detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18690,8 +19410,16 @@
           <t>6456943442-094-065570690344</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalafil SPI</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tadalafil SPI detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -18875,8 +19603,16 @@
           <t>8709575179-925-123723314126</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Toxefro</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Toxefro detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/59/file.xlsx
+++ b/product_upload/packages/59/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21444,7 +21444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21525,40 +21525,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21638,38 +21643,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>82.91</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-27DA815EEC57</t>
         </is>
@@ -21749,38 +21759,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>87.48</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-96E9CE159F2A</t>
         </is>
@@ -21860,38 +21875,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>202.27</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-CE306A7D139F</t>
         </is>
@@ -21971,38 +21991,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>362.48</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-B436946C9AA9</t>
         </is>
@@ -22082,38 +22107,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>412.49</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-EDABFC727E36</t>
         </is>
@@ -22193,38 +22223,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>196.1</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-A1338D7205FE</t>
         </is>
@@ -22304,38 +22339,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>271.82</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-F059534F1D83</t>
         </is>
@@ -22415,38 +22455,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>275.64</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-5D95E9805167</t>
         </is>
@@ -22526,38 +22571,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>352.47</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-798D34171280</t>
         </is>
@@ -22637,38 +22687,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>245.63</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-005E5AFE0F0B</t>
         </is>
@@ -22748,38 +22803,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>76.95</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-0CFF2333D771</t>
         </is>
@@ -22859,38 +22919,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>169.12</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-FF6DE2D7A9C9</t>
         </is>
@@ -22970,38 +23035,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>425.6</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-680F199BD42F</t>
         </is>
@@ -23081,38 +23151,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>347.41</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-3B2283BFE2ED</t>
         </is>
@@ -23192,38 +23267,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>371.06</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A8A07CC73DE9</t>
         </is>
@@ -23303,38 +23383,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>306.93</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-1A3765F39166</t>
         </is>
@@ -23414,38 +23499,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>106.3</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-A458F044142F</t>
         </is>
@@ -23525,38 +23615,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>375.06</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-DBE19EEBAEFE</t>
         </is>
@@ -23636,38 +23731,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>416.88</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-FF2FCA627438</t>
         </is>
@@ -23747,38 +23847,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>468.9</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-7AA33EB6950F</t>
         </is>
